--- a/mine/data/Excel/Blog.xlsx
+++ b/mine/data/Excel/Blog.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\MineGlobe\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\MineGlobe\mine\data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5121FC74-1271-45DD-A7C9-B4C94D231621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD29A64F-DC40-4A90-927F-B328824A2215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3849" yWindow="1843" windowWidth="16457" windowHeight="8426" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,15 +58,15 @@
     <t>Turn-based combat framework with modular deck architecture and scalable gameplay systems.</t>
   </si>
   <si>
-    <t>blog1.html</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CentOS 7系统下使用Docker安装elk</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Linux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blog/blog1.html</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -428,16 +428,16 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
         <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
